--- a/90_Output/AF_CPG_data_extraction_master_[작업자이름].xlsx
+++ b/90_Output/AF_CPG_data_extraction_master_[작업자이름].xlsx
@@ -470,10 +470,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU4"/>
+  <dimension ref="A1:AV4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
-    <col width="30" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="47" max="47"/>
+    <col width="30" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -708,6 +709,11 @@
         </is>
       </c>
       <c r="AU1" s="5" t="inlineStr">
+        <is>
+          <t>analysis_set</t>
+        </is>
+      </c>
+      <c r="AV1" s="5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/90_Output/AF_CPG_data_extraction_master_[작업자이름].xlsx
+++ b/90_Output/AF_CPG_data_extraction_master_[작업자이름].xlsx
@@ -9,6 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기본정보" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="아웃컴" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="한의중재_한약" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_meta" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -2234,4 +2235,70 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema_version</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>last_upgrade</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>last_actor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>